--- a/documentacion ejemplo/Planilla_trabajadores_ejemplo.xlsx
+++ b/documentacion ejemplo/Planilla_trabajadores_ejemplo.xlsx
@@ -2,27 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dragoneik\Desktop\APLICACIONES IA\Diario mural de turnos trabajadores\documentacion ejemplo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D876F7-E187-4F5D-ADE7-210694CE5F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC789005-10D5-410A-82DD-07ED3F5E564C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{936D50DD-AA64-4336-9F76-0714F2F1D78D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Catalogos" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$2:$J$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,15 +27,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
+  <si>
+    <t>EQUIPO DE TRABAJO</t>
+  </si>
   <si>
     <t>RUT</t>
   </si>
@@ -56,29 +49,287 @@
     <t>Apellido Materno</t>
   </si>
   <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>correo electronico</t>
+  </si>
+  <si>
+    <t>Sucursal</t>
+  </si>
+  <si>
     <t>Cargo</t>
   </si>
   <si>
-    <t>EQUIPO DE TRABAJO</t>
-  </si>
-  <si>
-    <t>telefono</t>
-  </si>
-  <si>
-    <t>correo electronico</t>
-  </si>
-  <si>
     <t>Clave de acceso</t>
   </si>
   <si>
-    <t>Sucursal</t>
+    <t>Iquique</t>
+  </si>
+  <si>
+    <t>Administrativo</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>Ejecutivos Dreams</t>
+  </si>
+  <si>
+    <t>Temuco</t>
+  </si>
+  <si>
+    <t>Valdivia</t>
+  </si>
+  <si>
+    <t>Punta Arenas</t>
+  </si>
+  <si>
+    <t>Sucursal Central</t>
+  </si>
+  <si>
+    <t>Sucursal Norte</t>
+  </si>
+  <si>
+    <t>21259968-9</t>
+  </si>
+  <si>
+    <t>Garrido</t>
+  </si>
+  <si>
+    <t>Monsalve</t>
+  </si>
+  <si>
+    <t>19978033-6</t>
+  </si>
+  <si>
+    <t>Fernanda Ignacia</t>
+  </si>
+  <si>
+    <t>Burloto</t>
+  </si>
+  <si>
+    <t>Nuñez</t>
+  </si>
+  <si>
+    <t>22482421-1</t>
+  </si>
+  <si>
+    <t>Leonor Anthonella</t>
+  </si>
+  <si>
+    <t>Pailamilla</t>
+  </si>
+  <si>
+    <t>Henriquez</t>
+  </si>
+  <si>
+    <t>21631161-2</t>
+  </si>
+  <si>
+    <t>Lorena Javiera</t>
+  </si>
+  <si>
+    <t>Andrade</t>
+  </si>
+  <si>
+    <t>Velásquez</t>
+  </si>
+  <si>
+    <t>25834738-2</t>
+  </si>
+  <si>
+    <t>Scarleth Meilyn</t>
+  </si>
+  <si>
+    <t>Tamburrino</t>
+  </si>
+  <si>
+    <t>Ortega</t>
+  </si>
+  <si>
+    <t>21028063-4</t>
+  </si>
+  <si>
+    <t>Murielle Mariane Fernanda</t>
+  </si>
+  <si>
+    <t>Fuentes</t>
+  </si>
+  <si>
+    <t>Riquelme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22075132-5 </t>
+  </si>
+  <si>
+    <t>Antonia Fernanda</t>
+  </si>
+  <si>
+    <t>Amaya</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>21088876-4</t>
+  </si>
+  <si>
+    <t>Escarlet Andrea</t>
+  </si>
+  <si>
+    <t>Hernandez</t>
+  </si>
+  <si>
+    <t>Vasquez</t>
+  </si>
+  <si>
+    <t>22480485-7</t>
+  </si>
+  <si>
+    <t>Martina Cecilia</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>Acevedo</t>
+  </si>
+  <si>
+    <t>18099197-2</t>
+  </si>
+  <si>
+    <t>Paola Angelica</t>
+  </si>
+  <si>
+    <t>Saez</t>
+  </si>
+  <si>
+    <t>21759432-4</t>
+  </si>
+  <si>
+    <t>Sofia Paz</t>
+  </si>
+  <si>
+    <t>Supanta</t>
+  </si>
+  <si>
+    <t>Paredes</t>
+  </si>
+  <si>
+    <t>20463658-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matias </t>
+  </si>
+  <si>
+    <t>Farfan</t>
+  </si>
+  <si>
+    <t>roa</t>
+  </si>
+  <si>
+    <t>dgarrisdo@gmail.com</t>
+  </si>
+  <si>
+    <t>fernanda.burloto98@gmail.com</t>
+  </si>
+  <si>
+    <t>lpailamillah@gmail.com</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>Loreandradev@gmail.com</t>
+  </si>
+  <si>
+    <t>tamburrinoscarleth02@gmail.com</t>
+  </si>
+  <si>
+    <t>CAMILA ROCIO</t>
+  </si>
+  <si>
+    <t>FONSECA</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>CESAR PATRICIO</t>
+  </si>
+  <si>
+    <t>INOSTROZA</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>EMELYN YANINA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>EGAÑA</t>
+  </si>
+  <si>
+    <t>18876267-0</t>
+  </si>
+  <si>
+    <t>21051221-7</t>
+  </si>
+  <si>
+    <t>21643011-5</t>
+  </si>
+  <si>
+    <t>Camila.fonsecacuevas@gmail.com</t>
+  </si>
+  <si>
+    <t>muri.mane.fuentes@gmail.com</t>
+  </si>
+  <si>
+    <t>cesarinostroza0089@gmail.com</t>
+  </si>
+  <si>
+    <t>emelyn.perezegana@gmail.com</t>
+  </si>
+  <si>
+    <t>antoniaamayaramos@gmail.com</t>
+  </si>
+  <si>
+    <t>paolasaez1963@gmail.com</t>
+  </si>
+  <si>
+    <t>matiasfarfan271@gmail.com</t>
+  </si>
+  <si>
+    <t>sofiasupanta.a@gmail.com</t>
+  </si>
+  <si>
+    <t>martina.cecilia23@gmail.com</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Diego Sebastian</t>
+  </si>
+  <si>
+    <t>Club Dreams</t>
+  </si>
+  <si>
+    <t>hernandezvasquezescarlet@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,23 +339,29 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -121,27 +378,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -151,75 +393,55 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -310,6 +532,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -344,6 +567,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -378,20 +602,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -513,246 +733,673 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DE95FC-4DB9-41CA-ABB9-FF4569017388}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="20.109375" customWidth="1"/>
-    <col min="8" max="8" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4">
+        <v>56972660465</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="2">
+        <v>56983524375</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4">
+        <v>56983587731</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4">
+        <v>56953234958</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="4">
+        <v>56941560665</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4">
+        <v>56994547498</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="8">
+        <v>56931453300</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="4">
+        <v>56946323525</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4">
+        <v>56952199691</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="4">
+        <v>56978348172</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4">
+        <v>56950230290</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="4">
+        <v>56964712405</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="4">
+        <v>56949053264</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="4">
+        <v>56927120692</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="4">
+        <v>56920207435</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="4">
+        <v>123456</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I3" xr:uid="{E6DE95FC-4DB9-41CA-ABB9-FF4569017388}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I15">
-      <sortCondition ref="H3"/>
+  <autoFilter ref="A2:J2" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:J17">
+      <sortCondition ref="H2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{0764B3A8-504E-4F3D-A50E-C23E358EF7C1}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{BB4383AE-BF17-4622-BAC0-D6A78934BE39}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{711E5368-CFCB-482F-8174-1BA7E5E5A023}"/>
+    <hyperlink ref="F12" r:id="rId4" xr:uid="{CD97C403-DFE0-46AD-8A47-A7D625BD95AC}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{58F02042-0A55-44C5-9649-EC8E4A2B4EA3}"/>
+    <hyperlink ref="F15" r:id="rId6" xr:uid="{9C6C7618-85B0-4720-99F6-CE658327F6E5}"/>
+    <hyperlink ref="F17" r:id="rId7" xr:uid="{4CCC0A0C-5936-4356-BD5A-0E83D1BCF1F2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Catalogos!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3 G18:G484</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>Catalogos!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>G3:G17 H10:H14 H16:H484 I3:I484</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>